--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DBD00B-B068-43CE-B6E3-6B91114EB4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3960EAF8-4E8D-43FA-BC08-8276A14A0560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Second Largest</t>
   </si>
@@ -58,6 +58,60 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>35. Search Insert Position</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>69. Sqrt(x)</t>
+  </si>
+  <si>
+    <t>509. Fibonacci Number</t>
+  </si>
+  <si>
+    <t>Rotate Array by One</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>268. Missing Number</t>
+  </si>
+  <si>
+    <t>Segregate 0s and 1s</t>
+  </si>
+  <si>
+    <t>Two Sum in Sorted Array</t>
+  </si>
+  <si>
+    <t>Find Pair Given Difference</t>
+  </si>
+  <si>
+    <t>easy+logical</t>
+  </si>
+  <si>
+    <t>Addition of two square matrices</t>
+  </si>
+  <si>
+    <t>Diagonal sum</t>
+  </si>
+  <si>
+    <t>basic +school</t>
+  </si>
+  <si>
+    <t>Print Matrix in Wave Form</t>
+  </si>
+  <si>
+    <t>867. Transpose Matrix</t>
+  </si>
+  <si>
+    <t>48. Rotate Image 90 degree</t>
+  </si>
+  <si>
+    <t>Rotate a Matrix by 180 Counterclockwise</t>
   </si>
 </sst>
 </file>
@@ -118,23 +172,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -450,18 +507,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="51.44140625" customWidth="1"/>
-    <col min="3" max="3" width="56.77734375" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18">
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -469,7 +527,7 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1"/>
@@ -478,7 +536,7 @@
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
@@ -487,15 +545,15 @@
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="18">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -503,7 +561,7 @@
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -511,7 +569,7 @@
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,39 +577,189 @@
       <c r="A8">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" ht="18">
       <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" ht="18">
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" ht="18">
       <c r="A11">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="C12" s="7"/>
+      <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" ht="18">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -564,6 +772,20 @@
     <hyperlink ref="B8" r:id="rId7" display="https://leetcode.com/problems/find-all-duplicates-in-an-array/" xr:uid="{8E2B30E7-4DA1-4292-80E8-178BDF1068B4}"/>
     <hyperlink ref="B9" r:id="rId8" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/" xr:uid="{80C751B4-D555-4EB4-B6B2-8790AF93C1C3}"/>
     <hyperlink ref="B10" r:id="rId9" xr:uid="{1513222E-918C-4C4B-A973-B9F53335151A}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://leetcode.com/problems/search-insert-position/" xr:uid="{732E9881-723D-4C00-93E3-8F6271936514}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://leetcode.com/problems/sqrtx/" xr:uid="{BC323EE0-239B-4769-B6E1-2A4899EA0F5A}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://leetcode.com/problems/fibonacci-number/" xr:uid="{51C695A7-95B6-48FD-BCB7-583CF5D5AD11}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{1801602D-0B19-4994-84E7-6807DD76F17A}"/>
+    <hyperlink ref="B15" r:id="rId14" display="https://leetcode.com/problems/missing-number/" xr:uid="{5D836DDF-B6C3-4455-B9F3-8C70D0CF732D}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{87E70035-4485-4709-95F4-04E8953D216C}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{225C9201-36F0-4784-B327-D380B9FF1745}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{AAEAEDBC-5F0A-43A7-9544-D9BB1EA359D8}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{3C16CF96-B90D-4823-BC29-89EE74D0A6AA}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{CE3B7277-6626-494F-B813-DCFB1FD696E4}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{7932E25B-A6A6-4BAD-BE7D-7F04090809B4}"/>
+    <hyperlink ref="B22" r:id="rId21" display="https://leetcode.com/problems/transpose-matrix/" xr:uid="{CC0224FD-958C-4A74-B335-D919B34FA81D}"/>
+    <hyperlink ref="B23" r:id="rId22" display="https://leetcode.com/problems/rotate-image/" xr:uid="{6140C280-EDD7-4042-9749-26DCB599B6EE}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{B6CF8BE7-2B0E-4B41-BB0D-6899BFEAE190}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3960EAF8-4E8D-43FA-BC08-8276A14A0560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8A8769-F98C-4705-9EA2-73E3BD018957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Second Largest</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Addition of two square matrices</t>
   </si>
   <si>
-    <t>Diagonal sum</t>
-  </si>
-  <si>
     <t>basic +school</t>
   </si>
   <si>
@@ -108,17 +105,41 @@
     <t>867. Transpose Matrix</t>
   </si>
   <si>
-    <t>48. Rotate Image 90 degree</t>
-  </si>
-  <si>
     <t>Rotate a Matrix by 180 Counterclockwise</t>
+  </si>
+  <si>
+    <t>74. Search a 2D Matrix</t>
+  </si>
+  <si>
+    <t>Diagonal sum of square matrix</t>
+  </si>
+  <si>
+    <t>48. Rotate Image 90 degree  clockwise</t>
+  </si>
+  <si>
+    <t>169. Majority Element</t>
+  </si>
+  <si>
+    <t>Missing And Repeating</t>
+  </si>
+  <si>
+    <t>153. Find Minimum in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>33. Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>1539. Kth Missing Positive Number</t>
+  </si>
+  <si>
+    <t>rohit and code story with mik</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,11 +159,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Sitka Heading"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF6A9955"/>
       <name val="Sitka Heading"/>
     </font>
     <font>
@@ -172,25 +188,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -507,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -553,7 +566,7 @@
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -565,11 +578,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -577,7 +590,7 @@
       <c r="A8">
         <v>8</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -585,7 +598,7 @@
       <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
@@ -596,7 +609,7 @@
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
@@ -607,7 +620,7 @@
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
@@ -618,10 +631,10 @@
       <c r="A12">
         <v>12</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="A13">
@@ -674,6 +687,9 @@
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" spans="1:3" ht="18">
       <c r="A18">
@@ -699,66 +715,132 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+    </row>
+    <row r="21" spans="1:3" ht="18">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18">
       <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>26</v>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" ht="18">
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>27</v>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" ht="18">
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>28</v>
+      <c r="B24" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" ht="18">
       <c r="A25">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="B25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18">
       <c r="A26">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="B26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18">
       <c r="A27">
         <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -781,11 +863,18 @@
     <hyperlink ref="B17" r:id="rId16" xr:uid="{225C9201-36F0-4784-B327-D380B9FF1745}"/>
     <hyperlink ref="B18" r:id="rId17" xr:uid="{AAEAEDBC-5F0A-43A7-9544-D9BB1EA359D8}"/>
     <hyperlink ref="B19" r:id="rId18" xr:uid="{3C16CF96-B90D-4823-BC29-89EE74D0A6AA}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{CE3B7277-6626-494F-B813-DCFB1FD696E4}"/>
+    <hyperlink ref="B20" r:id="rId19" display="Diagonal sum" xr:uid="{CE3B7277-6626-494F-B813-DCFB1FD696E4}"/>
     <hyperlink ref="B21" r:id="rId20" xr:uid="{7932E25B-A6A6-4BAD-BE7D-7F04090809B4}"/>
     <hyperlink ref="B22" r:id="rId21" display="https://leetcode.com/problems/transpose-matrix/" xr:uid="{CC0224FD-958C-4A74-B335-D919B34FA81D}"/>
     <hyperlink ref="B23" r:id="rId22" display="https://leetcode.com/problems/rotate-image/" xr:uid="{6140C280-EDD7-4042-9749-26DCB599B6EE}"/>
     <hyperlink ref="B24" r:id="rId23" xr:uid="{B6CF8BE7-2B0E-4B41-BB0D-6899BFEAE190}"/>
+    <hyperlink ref="B25" r:id="rId24" display="https://leetcode.com/problems/search-a-2d-matrix/" xr:uid="{0DA2BA2F-5018-4E93-85A9-421A9D73DE33}"/>
+    <hyperlink ref="B7" r:id="rId25" xr:uid="{2E2FD315-8A7F-4510-8AD2-4E68BA40933D}"/>
+    <hyperlink ref="B27" r:id="rId26" display="https://leetcode.com/problems/majority-element/" xr:uid="{2070CD96-0381-46F5-8BE3-FDE8D51E6E9A}"/>
+    <hyperlink ref="B26" r:id="rId27" xr:uid="{FEA549DB-6C5B-4996-9507-D21B68266633}"/>
+    <hyperlink ref="B28" r:id="rId28" display="https://leetcode.com/problems/find-minimum-in-rotated-sorted-array/" xr:uid="{F0279056-CE0E-477D-B68C-14A2DEDB3B10}"/>
+    <hyperlink ref="B29" r:id="rId29" display="https://leetcode.com/problems/search-in-rotated-sorted-array/" xr:uid="{8BE2CDBA-F97F-4575-971C-DBF9A8197F0F}"/>
+    <hyperlink ref="B30" r:id="rId30" display="https://leetcode.com/problems/kth-missing-positive-number/" xr:uid="{C6FBABBC-A896-42A1-9BB4-44E549F916A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8A8769-F98C-4705-9EA2-73E3BD018957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAAEF6-7C02-4AA7-BC0E-6080EA42F619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
   <si>
     <t>Second Largest</t>
   </si>
@@ -132,14 +132,35 @@
     <t>1539. Kth Missing Positive Number</t>
   </si>
   <si>
-    <t>rohit and code story with mik</t>
+    <t>easy+medium</t>
+  </si>
+  <si>
+    <t>189. Rotate Array k times clockwise</t>
+  </si>
+  <si>
+    <t>Allocate Minimum Pages</t>
+  </si>
+  <si>
+    <t>medium+hard</t>
+  </si>
+  <si>
+    <t>The Painter's Partition Problem-II</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>Aggressive Cows</t>
+  </si>
+  <si>
+    <t>875. Koko Eating Bananas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +187,13 @@
       <color theme="1"/>
       <name val="Stika h"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -188,9 +216,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -199,12 +226,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -520,11 +552,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="29.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -532,73 +564,95 @@
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:3" ht="18">
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="18">
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18">
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18">
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18">
       <c r="A8">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18">
       <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
@@ -609,7 +663,7 @@
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
@@ -620,7 +674,7 @@
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C11" t="s">
@@ -631,16 +685,18 @@
       <c r="A12">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="18">
       <c r="A13">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
@@ -651,7 +707,7 @@
       <c r="A14">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
@@ -662,7 +718,7 @@
       <c r="A15">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="s">
@@ -673,7 +729,7 @@
       <c r="A16">
         <v>16</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C16" t="s">
@@ -684,7 +740,7 @@
       <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
@@ -695,7 +751,7 @@
       <c r="A18">
         <v>18</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C18" t="s">
@@ -706,15 +762,18 @@
       <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18">
       <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C20" t="s">
@@ -725,15 +784,18 @@
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18">
       <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C22" t="s">
@@ -744,7 +806,7 @@
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C23" t="s">
@@ -755,7 +817,7 @@
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
@@ -766,7 +828,7 @@
       <c r="A25">
         <v>25</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C25" t="s">
@@ -777,7 +839,7 @@
       <c r="A26">
         <v>26</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C26" t="s">
@@ -788,14 +850,14 @@
       <c r="A27">
         <v>27</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" ht="18">
       <c r="A28">
         <v>28</v>
       </c>
@@ -806,7 +868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" ht="18">
       <c r="A29">
         <v>29</v>
       </c>
@@ -817,7 +879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" ht="18">
       <c r="A30">
         <v>30</v>
       </c>
@@ -828,19 +890,79 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" ht="18">
       <c r="A31">
         <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>33</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +996,12 @@
     <hyperlink ref="B26" r:id="rId27" xr:uid="{FEA549DB-6C5B-4996-9507-D21B68266633}"/>
     <hyperlink ref="B28" r:id="rId28" display="https://leetcode.com/problems/find-minimum-in-rotated-sorted-array/" xr:uid="{F0279056-CE0E-477D-B68C-14A2DEDB3B10}"/>
     <hyperlink ref="B29" r:id="rId29" display="https://leetcode.com/problems/search-in-rotated-sorted-array/" xr:uid="{8BE2CDBA-F97F-4575-971C-DBF9A8197F0F}"/>
-    <hyperlink ref="B30" r:id="rId30" display="https://leetcode.com/problems/kth-missing-positive-number/" xr:uid="{C6FBABBC-A896-42A1-9BB4-44E549F916A7}"/>
+    <hyperlink ref="B30" r:id="rId30" display="https://leetcode.com/problems/kth-missing-positive-number/" xr:uid="{FEEF71B4-5E22-494C-A141-AD93450FC97A}"/>
+    <hyperlink ref="B31" r:id="rId31" display="https://leetcode.com/problems/rotate-array/" xr:uid="{C90E024D-6BD3-487F-A573-3240E1FD737B}"/>
+    <hyperlink ref="B32" r:id="rId32" xr:uid="{AA71AA98-578D-4C7F-80C8-B8F306851713}"/>
+    <hyperlink ref="B33" r:id="rId33" xr:uid="{6F7ADA03-0528-4AD1-81EF-5EC880149FD1}"/>
+    <hyperlink ref="B34" r:id="rId34" xr:uid="{01123EC6-7693-428B-98AA-489A588E483F}"/>
+    <hyperlink ref="B35" r:id="rId35" display="https://leetcode.com/problems/koko-eating-bananas/" xr:uid="{09560A08-EED0-4294-B6B4-CEACC3290829}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAAEF6-7C02-4AA7-BC0E-6080EA42F619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB6956D-A434-4DD7-A125-42C70347743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>Second Largest</t>
   </si>
@@ -154,13 +154,28 @@
   </si>
   <si>
     <t>875. Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t>42. Trapping Rain Water</t>
+  </si>
+  <si>
+    <t>Four Elements</t>
+  </si>
+  <si>
+    <t>Triplet Sum in Array,  exists or not</t>
+  </si>
+  <si>
+    <t>15. There(3) Sum all distinct index</t>
+  </si>
+  <si>
+    <t>2016. Maximum Difference Between Increasing Elements</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +209,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Sitka Heading"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -216,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -230,13 +250,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -552,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -901,68 +915,119 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" ht="18">
       <c r="A32">
         <v>32</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" ht="18">
       <c r="A33">
         <v>33</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" ht="18">
       <c r="A34">
         <v>34</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" ht="18">
       <c r="A35">
         <v>35</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" ht="18">
       <c r="A36">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="B36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18">
       <c r="A37">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="B37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18">
       <c r="A38">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="B38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18">
       <c r="A39">
         <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1002,6 +1067,11 @@
     <hyperlink ref="B33" r:id="rId33" xr:uid="{6F7ADA03-0528-4AD1-81EF-5EC880149FD1}"/>
     <hyperlink ref="B34" r:id="rId34" xr:uid="{01123EC6-7693-428B-98AA-489A588E483F}"/>
     <hyperlink ref="B35" r:id="rId35" display="https://leetcode.com/problems/koko-eating-bananas/" xr:uid="{09560A08-EED0-4294-B6B4-CEACC3290829}"/>
+    <hyperlink ref="B36" r:id="rId36" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{3C9383E1-B517-450D-8740-1AE4CBDC7B66}"/>
+    <hyperlink ref="B37" r:id="rId37" display="Triplet Sum in Array" xr:uid="{CC17A172-130A-4D2B-8666-CFAE31C7E1DE}"/>
+    <hyperlink ref="B38" r:id="rId38" xr:uid="{920002F2-CE8A-413D-BFAD-7E3F0736F31A}"/>
+    <hyperlink ref="B40" r:id="rId39" display="https://leetcode.com/problems/maximum-difference-between-increasing-elements/" xr:uid="{2B48B52F-3A63-42AE-84F9-C03E455BF1D9}"/>
+    <hyperlink ref="B39" r:id="rId40" display="https://leetcode.com/problems/3sum/" xr:uid="{B409E310-0776-4495-A49F-3413B8E35141}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB6956D-A434-4DD7-A125-42C70347743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924B5BB1-54FE-45C1-9466-F8F091DEB7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
   <si>
     <t>Second Largest</t>
   </si>
@@ -159,23 +159,128 @@
     <t>42. Trapping Rain Water</t>
   </si>
   <si>
-    <t>Four Elements</t>
-  </si>
-  <si>
     <t>Triplet Sum in Array,  exists or not</t>
   </si>
   <si>
-    <t>15. There(3) Sum all distinct index</t>
-  </si>
-  <si>
     <t>2016. Maximum Difference Between Increasing Elements</t>
+  </si>
+  <si>
+    <t>Split an array into two equal Sum subarrays</t>
+  </si>
+  <si>
+    <t>maximum subarray sum using  Kadane's Algorithm</t>
+  </si>
+  <si>
+    <t>Four Elements sums equal to target</t>
+  </si>
+  <si>
+    <t>15. Three(3) Sum all distinct index equal to zero</t>
+  </si>
+  <si>
+    <t>Missing element of AP</t>
+  </si>
+  <si>
+    <t>Pythagorean Triplet</t>
+  </si>
+  <si>
+    <t>Equilibrium Point</t>
+  </si>
+  <si>
+    <t>Union of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>Three way partitioning</t>
+  </si>
+  <si>
+    <t>Greater on right side</t>
+  </si>
+  <si>
+    <t>Subarray with given sum</t>
+  </si>
+  <si>
+    <t>Frogs and Jumps</t>
+  </si>
+  <si>
+    <t>Rearrange Array Alternately</t>
+  </si>
+  <si>
+    <t>Rearrange an array with O(1) extra space</t>
+  </si>
+  <si>
+    <t>Boolean Matrix</t>
+  </si>
+  <si>
+    <t>Row with max 1s</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Maximum Triplet product</t>
+  </si>
+  <si>
+    <t>Coins of Geekland</t>
+  </si>
+  <si>
+    <t>Next Permutation</t>
+  </si>
+  <si>
+    <t>Rotate Image</t>
+  </si>
+  <si>
+    <t>Count Primes</t>
+  </si>
+  <si>
+    <t>Watering Plants</t>
+  </si>
+  <si>
+    <t>Arithmetic Subarrays</t>
+  </si>
+  <si>
+    <t>Max Circular Subarray Sum</t>
+  </si>
+  <si>
+    <t>Count the subarrays having product less than k</t>
+  </si>
+  <si>
+    <t>Maximum subset XOR</t>
+  </si>
+  <si>
+    <t>Next Smallest Palindrome</t>
+  </si>
+  <si>
+    <t>Count the number of subarrays</t>
+  </si>
+  <si>
+    <t>Largest rectangle of 1s with swapping of columns allowed</t>
+  </si>
+  <si>
+    <t>N/3 Repeat Number</t>
+  </si>
+  <si>
+    <t>easy + logical</t>
+  </si>
+  <si>
+    <t>easy very</t>
+  </si>
+  <si>
+    <t>medium+logical</t>
+  </si>
+  <si>
+    <t>easy SHEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smaller Than Triplet Sum</t>
+  </si>
+  <si>
+    <t>binary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,35 +303,64 @@
       <name val="Sitka Heading"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Stika h"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Sitka Heading"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Stika h"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -236,21 +370,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -566,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -581,7 +719,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -592,7 +730,7 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -603,7 +741,7 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -614,7 +752,7 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -622,10 +760,10 @@
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -636,7 +774,7 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -644,10 +782,10 @@
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -655,10 +793,10 @@
       <c r="A8">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -666,10 +804,10 @@
       <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -677,10 +815,10 @@
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -688,10 +826,10 @@
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -699,10 +837,10 @@
       <c r="A12">
         <v>12</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -713,7 +851,7 @@
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -724,7 +862,7 @@
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -735,7 +873,7 @@
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -746,7 +884,7 @@
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -757,7 +895,7 @@
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -768,7 +906,7 @@
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -779,7 +917,7 @@
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -790,7 +928,7 @@
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -798,10 +936,10 @@
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -812,7 +950,7 @@
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -823,7 +961,7 @@
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -834,7 +972,7 @@
       <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -845,7 +983,7 @@
       <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -856,7 +994,7 @@
       <c r="B26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -867,7 +1005,7 @@
       <c r="B27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -878,7 +1016,7 @@
       <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -889,7 +1027,7 @@
       <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -900,7 +1038,7 @@
       <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -911,7 +1049,7 @@
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -922,7 +1060,7 @@
       <c r="B32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="6" t="s">
         <v>38</v>
       </c>
     </row>
@@ -933,7 +1071,7 @@
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -941,10 +1079,10 @@
       <c r="A34">
         <v>34</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -955,7 +1093,7 @@
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -966,7 +1104,7 @@
       <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -975,9 +1113,9 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -986,9 +1124,9 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -997,9 +1135,9 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1008,26 +1146,286 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>41</v>
       </c>
-      <c r="B41" s="7"/>
+      <c r="B41" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <v>42</v>
       </c>
+      <c r="B42" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
         <v>43</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="18">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="18">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="18">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="18">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="18">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="18">
+      <c r="B70" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1069,10 +1467,41 @@
     <hyperlink ref="B35" r:id="rId35" display="https://leetcode.com/problems/koko-eating-bananas/" xr:uid="{09560A08-EED0-4294-B6B4-CEACC3290829}"/>
     <hyperlink ref="B36" r:id="rId36" display="https://leetcode.com/problems/trapping-rain-water/" xr:uid="{3C9383E1-B517-450D-8740-1AE4CBDC7B66}"/>
     <hyperlink ref="B37" r:id="rId37" display="Triplet Sum in Array" xr:uid="{CC17A172-130A-4D2B-8666-CFAE31C7E1DE}"/>
-    <hyperlink ref="B38" r:id="rId38" xr:uid="{920002F2-CE8A-413D-BFAD-7E3F0736F31A}"/>
+    <hyperlink ref="B38" r:id="rId38" display="Four Elements" xr:uid="{920002F2-CE8A-413D-BFAD-7E3F0736F31A}"/>
     <hyperlink ref="B40" r:id="rId39" display="https://leetcode.com/problems/maximum-difference-between-increasing-elements/" xr:uid="{2B48B52F-3A63-42AE-84F9-C03E455BF1D9}"/>
     <hyperlink ref="B39" r:id="rId40" display="https://leetcode.com/problems/3sum/" xr:uid="{B409E310-0776-4495-A49F-3413B8E35141}"/>
+    <hyperlink ref="B41" r:id="rId41" xr:uid="{B3B1645B-5744-42F6-B760-D16B5FE3B382}"/>
+    <hyperlink ref="B42" r:id="rId42" display="Kadane's Algorithm" xr:uid="{C55C1F96-E417-4399-AF38-996F467C9DCE}"/>
+    <hyperlink ref="B43" r:id="rId43" xr:uid="{43CDD0EE-1297-4019-8BDA-220AB4C80303}"/>
+    <hyperlink ref="B44" r:id="rId44" xr:uid="{CC23CBB3-8A56-47DC-8128-CAD01ADEBA72}"/>
+    <hyperlink ref="B45" r:id="rId45" xr:uid="{62061D0F-C291-46FB-89C3-9F6A9CD00C99}"/>
+    <hyperlink ref="B46" r:id="rId46" xr:uid="{EB9C0D14-6464-4D0E-BB33-3105F399B095}"/>
+    <hyperlink ref="B47" r:id="rId47" xr:uid="{0EAB221D-7E6B-49A4-AB4E-7106128D3612}"/>
+    <hyperlink ref="B48" r:id="rId48" xr:uid="{B4D6B095-7A1B-4343-B15C-7E743819B9D9}"/>
+    <hyperlink ref="B49" r:id="rId49" xr:uid="{CC845F4C-5FEE-4CB2-95DE-B67FEF86A66A}"/>
+    <hyperlink ref="B50" r:id="rId50" xr:uid="{360D4D69-BFB2-43F6-B0D1-84969D0D00A1}"/>
+    <hyperlink ref="B51" r:id="rId51" xr:uid="{F5668BC1-110E-4546-9AF1-3A4DA8B13A89}"/>
+    <hyperlink ref="B52" r:id="rId52" display="Count triplets with sum smaller than X" xr:uid="{589F78C7-ACC7-4F85-8F87-110AAABD9076}"/>
+    <hyperlink ref="B53" r:id="rId53" xr:uid="{7E492C05-D7EC-485B-B1AF-1AB0F817F7B1}"/>
+    <hyperlink ref="B54" r:id="rId54" xr:uid="{22B7693A-FFF7-42D9-AC11-FE795D2622A4}"/>
+    <hyperlink ref="B55" r:id="rId55" xr:uid="{3ECBB2E5-0C54-40C7-B326-652B6610FDD5}"/>
+    <hyperlink ref="B56" r:id="rId56" xr:uid="{7E3DEE61-5B25-4216-8AA3-39A04C5AAFE0}"/>
+    <hyperlink ref="B57" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
+    <hyperlink ref="B58" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
+    <hyperlink ref="B59" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
+    <hyperlink ref="B60" r:id="rId60" xr:uid="{93027393-03CE-4EB8-918E-F6F435C9B04B}"/>
+    <hyperlink ref="B61" r:id="rId61" xr:uid="{4A42692F-D72D-42DB-BE35-B30A9BDFEB16}"/>
+    <hyperlink ref="B62" r:id="rId62" xr:uid="{29C959BE-75F0-485B-B8C2-2FC68FD53868}"/>
+    <hyperlink ref="B63" r:id="rId63" xr:uid="{67087C73-7D08-48D0-9060-FA8E0F6A50AD}"/>
+    <hyperlink ref="B64" r:id="rId64" xr:uid="{54B91691-806E-4D1B-BCAD-710CB853A883}"/>
+    <hyperlink ref="B65" r:id="rId65" xr:uid="{468B0899-A951-4993-8E8A-342EA8E8F731}"/>
+    <hyperlink ref="B66" r:id="rId66" xr:uid="{25AAF2F4-1411-4145-80C4-A92DA586FC6C}"/>
+    <hyperlink ref="B67" r:id="rId67" xr:uid="{BB3105EF-EB98-4D41-B616-71A66E23CEF5}"/>
+    <hyperlink ref="B68" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
+    <hyperlink ref="B69" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
+    <hyperlink ref="B70" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId71"/>
 </worksheet>
 </file>
--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924B5BB1-54FE-45C1-9466-F8F091DEB7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB41E967-51B2-4BC4-BB33-1C65CAFAC3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
   <si>
     <t>Second Largest</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Row with max 1s</t>
   </si>
   <si>
-    <t>Container With Most Water</t>
-  </si>
-  <si>
     <t>Maximum Triplet product</t>
   </si>
   <si>
@@ -274,13 +271,73 @@
   </si>
   <si>
     <t>binary</t>
+  </si>
+  <si>
+    <t>11 Container With Most Water</t>
+  </si>
+  <si>
+    <t>Reverse a String</t>
+  </si>
+  <si>
+    <t>1108. Defanging an IP Address</t>
+  </si>
+  <si>
+    <t>Palindrome String</t>
+  </si>
+  <si>
+    <t>Rotate clockwise string</t>
+  </si>
+  <si>
+    <t>Rotate anticlock wise</t>
+  </si>
+  <si>
+    <t>String Rotated by 2 Places</t>
+  </si>
+  <si>
+    <t>1832. Check if the Sentence Is Pangram</t>
+  </si>
+  <si>
+    <t>Sort a String</t>
+  </si>
+  <si>
+    <t>409. Longest Palindrome</t>
+  </si>
+  <si>
+    <t>1859. Sorting the Sentence</t>
+  </si>
+  <si>
+    <t>Sum of two large numbers</t>
+  </si>
+  <si>
+    <t>Roman Number to Integer</t>
+  </si>
+  <si>
+    <t>Factorial using different logic</t>
+  </si>
+  <si>
+    <t>3. Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Smallest distinct window</t>
+  </si>
+  <si>
+    <t>Longest Prefix Suffix : KMP algorithm</t>
+  </si>
+  <si>
+    <t>28. Find the Index of the First Occurrence in a String</t>
+  </si>
+  <si>
+    <t>Min Chars to Add for Palindrome</t>
+  </si>
+  <si>
+    <t>686. Repeated String Match</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,15 +363,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
-      <name val="Stika h"/>
+      <name val="Poppins"/>
     </font>
   </fonts>
   <fills count="3">
@@ -331,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -354,23 +403,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -385,10 +423,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -704,728 +741,910 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:D70"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D104"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
     <col min="3" max="3" width="29.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A1">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18">
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18">
+      <c r="C2" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18">
+      <c r="C3" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18">
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18">
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18">
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18">
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18">
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18">
+      <c r="C9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18">
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A11">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18">
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A12">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18">
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A13">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18">
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A14">
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18">
+    <row r="15" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A15">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18">
+      <c r="C15" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A16">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18">
+      <c r="C16" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18">
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18">
+    <row r="19" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18">
+      <c r="C19" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18">
+    <row r="21" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18">
+      <c r="C21" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18">
+      <c r="C22" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="18">
+      <c r="C23" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18">
+      <c r="C24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="18">
+      <c r="C25" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="18">
+      <c r="C26" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="18">
+      <c r="C27" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18">
+      <c r="C28" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A29">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="18">
+      <c r="C29" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A30">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18">
+    <row r="31" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A31">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="18">
+      <c r="C31" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A32">
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18">
+    <row r="33" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A33">
         <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18">
+    <row r="34" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A34">
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="18">
+      <c r="C34" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A35">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="18">
+      <c r="C35" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A36">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18">
+    <row r="37" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A37">
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="18">
+      <c r="C37" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A38">
         <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="18">
+      <c r="C38" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A39">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="18">
+      <c r="C39" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="21" x14ac:dyDescent="0.7">
       <c r="A40">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A41">
         <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="C41" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A42">
         <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="C42" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A43">
         <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="C43" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A44">
         <v>44</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="C44" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A45">
         <v>45</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="C45" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A46">
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="C46" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A47">
         <v>47</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="C47" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A48">
         <v>48</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="C48" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A49">
         <v>49</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="C49" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A50">
         <v>50</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A51">
         <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="C51" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A52">
         <v>52</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+    </row>
+    <row r="53" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A53">
         <v>53</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="C53" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A54">
         <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="C54" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A55">
         <v>55</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="C55" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A56">
         <v>56</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="18">
+        <v>82</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="18">
+        <v>62</v>
+      </c>
+      <c r="C57" s="6"/>
+    </row>
+    <row r="58" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="18">
+        <v>63</v>
+      </c>
+      <c r="C58" s="6"/>
+    </row>
+    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>59</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="18">
+        <v>64</v>
+      </c>
+      <c r="C59" s="6"/>
+    </row>
+    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>60</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="18">
+        <v>65</v>
+      </c>
+      <c r="C60" s="6"/>
+    </row>
+    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="18">
+        <v>66</v>
+      </c>
+      <c r="C61" s="6"/>
+    </row>
+    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18">
+        <v>67</v>
+      </c>
+      <c r="C62" s="6"/>
+    </row>
+    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>63</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="18">
+        <v>68</v>
+      </c>
+      <c r="C63" s="6"/>
+    </row>
+    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>64</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="18">
+        <v>69</v>
+      </c>
+      <c r="C64" s="6"/>
+    </row>
+    <row r="65" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="18">
+        <v>70</v>
+      </c>
+      <c r="C65" s="6"/>
+    </row>
+    <row r="66" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>66</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="18">
+        <v>71</v>
+      </c>
+      <c r="C66" s="6"/>
+    </row>
+    <row r="67" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>67</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="18">
+        <v>72</v>
+      </c>
+      <c r="C67" s="6"/>
+    </row>
+    <row r="68" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>68</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="18">
+        <v>73</v>
+      </c>
+      <c r="C68" s="6"/>
+    </row>
+    <row r="69" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>69</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="6"/>
+    </row>
+    <row r="70" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B70" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="18">
-      <c r="B70" s="2" t="s">
-        <v>76</v>
+    <row r="85" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>2</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>4</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>5</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>7</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>8</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>9</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>10</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>11</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>12</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>13</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>14</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>15</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>16</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>17</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>18</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>19</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1704,7 @@
     <hyperlink ref="B53" r:id="rId53" xr:uid="{7E492C05-D7EC-485B-B1AF-1AB0F817F7B1}"/>
     <hyperlink ref="B54" r:id="rId54" xr:uid="{22B7693A-FFF7-42D9-AC11-FE795D2622A4}"/>
     <hyperlink ref="B55" r:id="rId55" xr:uid="{3ECBB2E5-0C54-40C7-B326-652B6610FDD5}"/>
-    <hyperlink ref="B56" r:id="rId56" xr:uid="{7E3DEE61-5B25-4216-8AA3-39A04C5AAFE0}"/>
+    <hyperlink ref="B56" r:id="rId56" display="Container With Most Water" xr:uid="{7E3DEE61-5B25-4216-8AA3-39A04C5AAFE0}"/>
     <hyperlink ref="B57" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
     <hyperlink ref="B58" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
     <hyperlink ref="B59" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
@@ -1500,8 +1719,25 @@
     <hyperlink ref="B68" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
     <hyperlink ref="B69" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
     <hyperlink ref="B70" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
+    <hyperlink ref="B85" r:id="rId71" xr:uid="{CE309F08-AAC1-410D-8FF0-E7A7D5A30A1D}"/>
+    <hyperlink ref="B86" r:id="rId72" display="https://leetcode.com/problems/defanging-an-ip-address/" xr:uid="{61E13826-11D6-4ECB-BB7F-1CFA1CBC0F4A}"/>
+    <hyperlink ref="B87" r:id="rId73" xr:uid="{1A07F699-F5A6-4748-A976-593E0232604E}"/>
+    <hyperlink ref="B90" r:id="rId74" xr:uid="{2D3F5BC2-ED14-465B-9382-86BCCD107FD5}"/>
+    <hyperlink ref="B91" r:id="rId75" display="https://leetcode.com/problems/check-if-the-sentence-is-pangram/" xr:uid="{554A218C-8662-4AC2-8F6B-2BD542582755}"/>
+    <hyperlink ref="B92" r:id="rId76" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
+    <hyperlink ref="B93" r:id="rId77" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
+    <hyperlink ref="B94" r:id="rId78" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
+    <hyperlink ref="B95" r:id="rId79" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
+    <hyperlink ref="B96" r:id="rId80" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
+    <hyperlink ref="B97" r:id="rId81" display="Factorial" xr:uid="{E8A4A4A4-3F2B-4E9A-B4D0-2FE2BD539289}"/>
+    <hyperlink ref="B98" r:id="rId82" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
+    <hyperlink ref="B99" r:id="rId83" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
+    <hyperlink ref="B100" r:id="rId84" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
+    <hyperlink ref="B101" r:id="rId85" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
+    <hyperlink ref="B102" r:id="rId86" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
+    <hyperlink ref="B103" r:id="rId87" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId71"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
 </worksheet>
 </file>
--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB41E967-51B2-4BC4-BB33-1C65CAFAC3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68E03D1-7982-4A0A-B237-E94E74C16C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
   <si>
     <t>Second Largest</t>
   </si>
@@ -285,12 +285,6 @@
     <t>Palindrome String</t>
   </si>
   <si>
-    <t>Rotate clockwise string</t>
-  </si>
-  <si>
-    <t>Rotate anticlock wise</t>
-  </si>
-  <si>
     <t>String Rotated by 2 Places</t>
   </si>
   <si>
@@ -306,15 +300,6 @@
     <t>1859. Sorting the Sentence</t>
   </si>
   <si>
-    <t>Sum of two large numbers</t>
-  </si>
-  <si>
-    <t>Roman Number to Integer</t>
-  </si>
-  <si>
-    <t>Factorial using different logic</t>
-  </si>
-  <si>
     <t>3. Longest Substring Without Repeating Characters</t>
   </si>
   <si>
@@ -331,6 +316,27 @@
   </si>
   <si>
     <t>686. Repeated String Match</t>
+  </si>
+  <si>
+    <t>rotate a charatcter in string clockwise</t>
+  </si>
+  <si>
+    <t>rotate a charatcter in string anticlock wise</t>
+  </si>
+  <si>
+    <t>2785. Sort Vowels in a String</t>
+  </si>
+  <si>
+    <t>415. Add Strings</t>
+  </si>
+  <si>
+    <t>Factorials of large numbers</t>
+  </si>
+  <si>
+    <t>13. Roman to Integer(Decimal)</t>
+  </si>
+  <si>
+    <t>12. Integer(Decimal) to Roman</t>
   </si>
 </sst>
 </file>
@@ -380,7 +386,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -403,12 +409,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -426,6 +443,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -741,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -1490,161 +1509,219 @@
         <v>75</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A85">
         <v>1</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="C85" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A86">
         <v>2</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="C86" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A87">
         <v>3</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="C87" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A88">
         <v>4</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A89">
         <v>5</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A90">
         <v>6</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A91">
         <v>7</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A92">
         <v>8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A93">
         <v>9</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A94">
         <v>10</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A95">
         <v>11</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A96">
         <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A97">
         <v>13</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B97" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A98">
         <v>14</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B98" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>15</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B99" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>16</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B100" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>17</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>18</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B102" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>19</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>20</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>21</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1727,17 +1804,19 @@
     <hyperlink ref="B92" r:id="rId76" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
     <hyperlink ref="B93" r:id="rId77" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
     <hyperlink ref="B94" r:id="rId78" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
-    <hyperlink ref="B95" r:id="rId79" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
-    <hyperlink ref="B96" r:id="rId80" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
-    <hyperlink ref="B97" r:id="rId81" display="Factorial" xr:uid="{E8A4A4A4-3F2B-4E9A-B4D0-2FE2BD539289}"/>
-    <hyperlink ref="B98" r:id="rId82" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
-    <hyperlink ref="B99" r:id="rId83" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
-    <hyperlink ref="B100" r:id="rId84" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
-    <hyperlink ref="B101" r:id="rId85" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
-    <hyperlink ref="B102" r:id="rId86" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
-    <hyperlink ref="B103" r:id="rId87" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
+    <hyperlink ref="B96" r:id="rId79" display="Sum of two large numbers" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
+    <hyperlink ref="B97" r:id="rId80" display="13. Roman to Integer" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
+    <hyperlink ref="B100" r:id="rId81" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
+    <hyperlink ref="B101" r:id="rId82" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
+    <hyperlink ref="B102" r:id="rId83" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
+    <hyperlink ref="B103" r:id="rId84" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
+    <hyperlink ref="B104" r:id="rId85" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
+    <hyperlink ref="B105" r:id="rId86" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
+    <hyperlink ref="B95" r:id="rId87" display="https://leetcode.com/problems/sort-vowels-in-a-string/" xr:uid="{54E1491C-52FF-4A5F-919A-377E24189B75}"/>
+    <hyperlink ref="B98" r:id="rId88" display="https://leetcode.com/problems/integer-to-roman/" xr:uid="{87FF45BE-8E25-4645-9BEE-BF58CB0ACE49}"/>
+    <hyperlink ref="B99" r:id="rId89" xr:uid="{C73FEF19-EB93-4B48-8546-CC067904474D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
 </worksheet>
 </file>
--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68E03D1-7982-4A0A-B237-E94E74C16C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85801A84-D92A-4625-9F76-A8337C7B2B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="108">
   <si>
     <t>Second Largest</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Sort a String</t>
   </si>
   <si>
-    <t>409. Longest Palindrome</t>
-  </si>
-  <si>
     <t>1859. Sorting the Sentence</t>
   </si>
   <si>
@@ -337,6 +334,21 @@
   </si>
   <si>
     <t>12. Integer(Decimal) to Roman</t>
+  </si>
+  <si>
+    <t>409. Longest Palindrome length</t>
+  </si>
+  <si>
+    <t>4. Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>134. Gas Station</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>**</t>
   </si>
 </sst>
 </file>
@@ -760,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -1387,156 +1399,123 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A57">
         <v>57</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="6"/>
-    </row>
-    <row r="58" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B57" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A58">
         <v>58</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="6"/>
+    </row>
+    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B60" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="6"/>
-    </row>
-    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>59</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="6"/>
+    </row>
+    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="6"/>
-    </row>
-    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>60</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="6"/>
+    </row>
+    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B62" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C60" s="6"/>
-    </row>
-    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>61</v>
-      </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="6"/>
+    </row>
+    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="6"/>
-    </row>
-    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>62</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="C63" s="6"/>
+      <c r="D63" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B64" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="6"/>
-    </row>
-    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>63</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C64" s="6"/>
+    </row>
+    <row r="65" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B65" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="6"/>
-    </row>
-    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>64</v>
-      </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="6"/>
+    </row>
+    <row r="66" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B66" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="6"/>
-    </row>
-    <row r="65" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>65</v>
-      </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="6"/>
+    </row>
+    <row r="67" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B67" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="6"/>
-    </row>
-    <row r="66" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>66</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="6"/>
+    </row>
+    <row r="68" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B68" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="6"/>
-    </row>
-    <row r="67" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>67</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="6"/>
+    </row>
+    <row r="69" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B69" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C67" s="6"/>
-    </row>
-    <row r="68" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>68</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="C69" s="6"/>
+    </row>
+    <row r="70" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B70" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="6"/>
-    </row>
-    <row r="69" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>69</v>
-      </c>
-      <c r="B69" s="2" t="s">
+      <c r="C70" s="6"/>
+    </row>
+    <row r="71" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B71" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="6"/>
-    </row>
-    <row r="70" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B70" s="2" t="s">
+      <c r="C71" s="6"/>
+    </row>
+    <row r="72" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B72" s="2" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A85">
-        <v>1</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A86">
-        <v>2</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>12</v>
@@ -1544,10 +1523,10 @@
     </row>
     <row r="88" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A88">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>12</v>
@@ -1555,10 +1534,10 @@
     </row>
     <row r="89" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A89">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>12</v>
@@ -1566,21 +1545,21 @@
     </row>
     <row r="90" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A90">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A91">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>12</v>
@@ -1588,43 +1567,43 @@
     </row>
     <row r="92" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A93">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A94">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A95">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>10</v>
@@ -1632,95 +1611,132 @@
     </row>
     <row r="96" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A96">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A97">
-        <v>13</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A98">
-        <v>14</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A99">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="C99" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A100">
+        <v>14</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A101">
+        <v>15</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A102">
         <v>16</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A103">
+        <v>17</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>17</v>
-      </c>
-      <c r="B101" s="2" t="s">
+      <c r="C103" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A104">
+        <v>18</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>18</v>
-      </c>
-      <c r="B102" s="5" t="s">
+      <c r="C104" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A105">
+        <v>19</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>19</v>
-      </c>
-      <c r="B103" s="2" t="s">
+      <c r="C105" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>20</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>20</v>
-      </c>
-      <c r="B104" s="2" t="s">
+    <row r="107" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>21</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>21</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108">
         <v>21</v>
       </c>
     </row>
@@ -1782,41 +1798,43 @@
     <hyperlink ref="B54" r:id="rId54" xr:uid="{22B7693A-FFF7-42D9-AC11-FE795D2622A4}"/>
     <hyperlink ref="B55" r:id="rId55" xr:uid="{3ECBB2E5-0C54-40C7-B326-652B6610FDD5}"/>
     <hyperlink ref="B56" r:id="rId56" display="Container With Most Water" xr:uid="{7E3DEE61-5B25-4216-8AA3-39A04C5AAFE0}"/>
-    <hyperlink ref="B57" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
-    <hyperlink ref="B58" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
-    <hyperlink ref="B59" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
-    <hyperlink ref="B60" r:id="rId60" xr:uid="{93027393-03CE-4EB8-918E-F6F435C9B04B}"/>
-    <hyperlink ref="B61" r:id="rId61" xr:uid="{4A42692F-D72D-42DB-BE35-B30A9BDFEB16}"/>
-    <hyperlink ref="B62" r:id="rId62" xr:uid="{29C959BE-75F0-485B-B8C2-2FC68FD53868}"/>
-    <hyperlink ref="B63" r:id="rId63" xr:uid="{67087C73-7D08-48D0-9060-FA8E0F6A50AD}"/>
-    <hyperlink ref="B64" r:id="rId64" xr:uid="{54B91691-806E-4D1B-BCAD-710CB853A883}"/>
-    <hyperlink ref="B65" r:id="rId65" xr:uid="{468B0899-A951-4993-8E8A-342EA8E8F731}"/>
-    <hyperlink ref="B66" r:id="rId66" xr:uid="{25AAF2F4-1411-4145-80C4-A92DA586FC6C}"/>
-    <hyperlink ref="B67" r:id="rId67" xr:uid="{BB3105EF-EB98-4D41-B616-71A66E23CEF5}"/>
-    <hyperlink ref="B68" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
-    <hyperlink ref="B69" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
-    <hyperlink ref="B70" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
-    <hyperlink ref="B85" r:id="rId71" xr:uid="{CE309F08-AAC1-410D-8FF0-E7A7D5A30A1D}"/>
-    <hyperlink ref="B86" r:id="rId72" display="https://leetcode.com/problems/defanging-an-ip-address/" xr:uid="{61E13826-11D6-4ECB-BB7F-1CFA1CBC0F4A}"/>
-    <hyperlink ref="B87" r:id="rId73" xr:uid="{1A07F699-F5A6-4748-A976-593E0232604E}"/>
-    <hyperlink ref="B90" r:id="rId74" xr:uid="{2D3F5BC2-ED14-465B-9382-86BCCD107FD5}"/>
-    <hyperlink ref="B91" r:id="rId75" display="https://leetcode.com/problems/check-if-the-sentence-is-pangram/" xr:uid="{554A218C-8662-4AC2-8F6B-2BD542582755}"/>
-    <hyperlink ref="B92" r:id="rId76" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
-    <hyperlink ref="B93" r:id="rId77" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
-    <hyperlink ref="B94" r:id="rId78" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
-    <hyperlink ref="B96" r:id="rId79" display="Sum of two large numbers" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
-    <hyperlink ref="B97" r:id="rId80" display="13. Roman to Integer" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
-    <hyperlink ref="B100" r:id="rId81" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
-    <hyperlink ref="B101" r:id="rId82" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
-    <hyperlink ref="B102" r:id="rId83" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
-    <hyperlink ref="B103" r:id="rId84" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
-    <hyperlink ref="B104" r:id="rId85" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
-    <hyperlink ref="B105" r:id="rId86" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
-    <hyperlink ref="B95" r:id="rId87" display="https://leetcode.com/problems/sort-vowels-in-a-string/" xr:uid="{54E1491C-52FF-4A5F-919A-377E24189B75}"/>
-    <hyperlink ref="B98" r:id="rId88" display="https://leetcode.com/problems/integer-to-roman/" xr:uid="{87FF45BE-8E25-4645-9BEE-BF58CB0ACE49}"/>
-    <hyperlink ref="B99" r:id="rId89" xr:uid="{C73FEF19-EB93-4B48-8546-CC067904474D}"/>
+    <hyperlink ref="B59" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
+    <hyperlink ref="B60" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
+    <hyperlink ref="B61" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
+    <hyperlink ref="B62" r:id="rId60" xr:uid="{93027393-03CE-4EB8-918E-F6F435C9B04B}"/>
+    <hyperlink ref="B63" r:id="rId61" xr:uid="{4A42692F-D72D-42DB-BE35-B30A9BDFEB16}"/>
+    <hyperlink ref="B64" r:id="rId62" xr:uid="{29C959BE-75F0-485B-B8C2-2FC68FD53868}"/>
+    <hyperlink ref="B65" r:id="rId63" xr:uid="{67087C73-7D08-48D0-9060-FA8E0F6A50AD}"/>
+    <hyperlink ref="B66" r:id="rId64" xr:uid="{54B91691-806E-4D1B-BCAD-710CB853A883}"/>
+    <hyperlink ref="B67" r:id="rId65" xr:uid="{468B0899-A951-4993-8E8A-342EA8E8F731}"/>
+    <hyperlink ref="B68" r:id="rId66" xr:uid="{25AAF2F4-1411-4145-80C4-A92DA586FC6C}"/>
+    <hyperlink ref="B69" r:id="rId67" xr:uid="{BB3105EF-EB98-4D41-B616-71A66E23CEF5}"/>
+    <hyperlink ref="B70" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
+    <hyperlink ref="B71" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
+    <hyperlink ref="B72" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
+    <hyperlink ref="B87" r:id="rId71" xr:uid="{CE309F08-AAC1-410D-8FF0-E7A7D5A30A1D}"/>
+    <hyperlink ref="B88" r:id="rId72" display="https://leetcode.com/problems/defanging-an-ip-address/" xr:uid="{61E13826-11D6-4ECB-BB7F-1CFA1CBC0F4A}"/>
+    <hyperlink ref="B89" r:id="rId73" xr:uid="{1A07F699-F5A6-4748-A976-593E0232604E}"/>
+    <hyperlink ref="B92" r:id="rId74" xr:uid="{2D3F5BC2-ED14-465B-9382-86BCCD107FD5}"/>
+    <hyperlink ref="B93" r:id="rId75" display="https://leetcode.com/problems/check-if-the-sentence-is-pangram/" xr:uid="{554A218C-8662-4AC2-8F6B-2BD542582755}"/>
+    <hyperlink ref="B94" r:id="rId76" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
+    <hyperlink ref="B95" r:id="rId77" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
+    <hyperlink ref="B96" r:id="rId78" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
+    <hyperlink ref="B98" r:id="rId79" display="Sum of two large numbers" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
+    <hyperlink ref="B99" r:id="rId80" display="13. Roman to Integer" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
+    <hyperlink ref="B102" r:id="rId81" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
+    <hyperlink ref="B103" r:id="rId82" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
+    <hyperlink ref="B104" r:id="rId83" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
+    <hyperlink ref="B105" r:id="rId84" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
+    <hyperlink ref="B106" r:id="rId85" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
+    <hyperlink ref="B107" r:id="rId86" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
+    <hyperlink ref="B97" r:id="rId87" display="https://leetcode.com/problems/sort-vowels-in-a-string/" xr:uid="{54E1491C-52FF-4A5F-919A-377E24189B75}"/>
+    <hyperlink ref="B100" r:id="rId88" display="https://leetcode.com/problems/integer-to-roman/" xr:uid="{87FF45BE-8E25-4645-9BEE-BF58CB0ACE49}"/>
+    <hyperlink ref="B101" r:id="rId89" xr:uid="{C73FEF19-EB93-4B48-8546-CC067904474D}"/>
+    <hyperlink ref="B57" r:id="rId90" display="https://leetcode.com/problems/median-of-two-sorted-arrays/" xr:uid="{A225C855-05F6-475F-9D5F-8F2E2142AF40}"/>
+    <hyperlink ref="B58" r:id="rId91" display="https://leetcode.com/problems/gas-station/" xr:uid="{B36E0DAE-16CC-42AF-82FD-1761D3574939}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId90"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId92"/>
 </worksheet>
 </file>
--- a/my_sheet.xlsx
+++ b/my_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dsa_question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85801A84-D92A-4625-9F76-A8337C7B2B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9B9DD-2B19-44AA-A674-166F66B86AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AF2AF579-E7B0-458D-B901-0DB6647B413C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="117">
   <si>
     <t>Second Largest</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Rotate a Matrix by 180 Counterclockwise</t>
   </si>
   <si>
-    <t>74. Search a 2D Matrix</t>
-  </si>
-  <si>
     <t>Diagonal sum of square matrix</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t xml:space="preserve"> Smaller Than Triplet Sum</t>
   </si>
   <si>
-    <t>binary</t>
-  </si>
-  <si>
     <t>11 Container With Most Water</t>
   </si>
   <si>
@@ -349,6 +343,39 @@
   </si>
   <si>
     <t>**</t>
+  </si>
+  <si>
+    <t>print linked list</t>
+  </si>
+  <si>
+    <t>array to linked list</t>
+  </si>
+  <si>
+    <t>Linked List Insertion At Beginning</t>
+  </si>
+  <si>
+    <t>Linked List Insertion At End</t>
+  </si>
+  <si>
+    <t>Insertion at a Given Position in a Linked List</t>
+  </si>
+  <si>
+    <t>Count nodes of linked list</t>
+  </si>
+  <si>
+    <t>Delete in a Singly Linked List</t>
+  </si>
+  <si>
+    <t>Reverse a linked list</t>
+  </si>
+  <si>
+    <t>74. Search a 2D Matrix  (row is sorted )</t>
+  </si>
+  <si>
+    <t>binary search</t>
+  </si>
+  <si>
+    <t>Decimal to binary</t>
   </si>
 </sst>
 </file>
@@ -437,7 +464,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -457,6 +484,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -772,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1726F5F5-5917-49CC-A3F2-3868F98A5482}">
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -780,7 +808,7 @@
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A1">
         <v>1</v>
       </c>
@@ -791,7 +819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A2">
         <v>2</v>
       </c>
@@ -802,7 +830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A3">
         <v>3</v>
       </c>
@@ -813,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A4">
         <v>4</v>
       </c>
@@ -824,7 +852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A5">
         <v>5</v>
       </c>
@@ -835,7 +863,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A6">
         <v>6</v>
       </c>
@@ -846,7 +874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A7">
         <v>7</v>
       </c>
@@ -857,7 +885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A8">
         <v>8</v>
       </c>
@@ -868,7 +896,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A9">
         <v>9</v>
       </c>
@@ -878,8 +906,11 @@
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A10">
         <v>10</v>
       </c>
@@ -889,8 +920,11 @@
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="D10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A11">
         <v>11</v>
       </c>
@@ -900,8 +934,11 @@
       <c r="C11" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A12">
         <v>12</v>
       </c>
@@ -911,8 +948,11 @@
       <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A13">
         <v>13</v>
       </c>
@@ -923,7 +963,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A14">
         <v>14</v>
       </c>
@@ -934,7 +974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A15">
         <v>15</v>
       </c>
@@ -945,7 +985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A16">
         <v>16</v>
       </c>
@@ -956,7 +996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A17">
         <v>17</v>
       </c>
@@ -967,7 +1007,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="18" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A18">
         <v>18</v>
       </c>
@@ -978,7 +1018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A19">
         <v>19</v>
       </c>
@@ -989,18 +1029,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1011,7 +1051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="22" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1022,18 +1062,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="24" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1044,92 +1084,101 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="26" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="27" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+    <row r="28" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+      <c r="D28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A29">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A30">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="21" x14ac:dyDescent="0.7">
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="21" x14ac:dyDescent="0.7">
       <c r="A31">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+    <row r="32" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
       <c r="A32">
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1137,10 +1186,10 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1148,7 +1197,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>10</v>
@@ -1159,7 +1208,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>10</v>
@@ -1170,10 +1219,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1181,7 +1230,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>12</v>
@@ -1192,7 +1241,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>12</v>
@@ -1203,7 +1252,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>10</v>
@@ -1214,7 +1263,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>21</v>
@@ -1225,7 +1274,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>12</v>
@@ -1236,7 +1285,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>10</v>
@@ -1247,10 +1296,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1258,7 +1307,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>10</v>
@@ -1269,10 +1318,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1280,7 +1329,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>10</v>
@@ -1291,10 +1340,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1302,10 +1351,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1313,10 +1362,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1324,7 +1373,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>21</v>
@@ -1335,7 +1384,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>10</v>
@@ -1346,13 +1395,13 @@
         <v>52</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1360,7 +1409,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>12</v>
@@ -1371,7 +1420,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>10</v>
@@ -1382,7 +1431,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>10</v>
@@ -1393,7 +1442,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>10</v>
@@ -1404,10 +1453,10 @@
         <v>57</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
@@ -1415,330 +1464,432 @@
         <v>58</v>
       </c>
       <c r="B58" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B82" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="6"/>
+    </row>
+    <row r="83" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B83" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" s="6"/>
+    </row>
+    <row r="84" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B84" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="6"/>
+    </row>
+    <row r="85" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B85" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" s="6"/>
+    </row>
+    <row r="86" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B59" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="6"/>
-    </row>
-    <row r="60" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B60" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="6"/>
-    </row>
-    <row r="61" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B61" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="6"/>
-    </row>
-    <row r="62" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B62" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="6"/>
-    </row>
-    <row r="63" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="C86" s="6"/>
+      <c r="D86" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B87" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" s="6"/>
+    </row>
+    <row r="88" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="6"/>
+    </row>
+    <row r="89" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B89" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" s="6"/>
+    </row>
+    <row r="90" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B90" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C90" s="6"/>
+    </row>
+    <row r="91" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B91" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="6"/>
+    </row>
+    <row r="92" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B92" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C92" s="6"/>
+    </row>
+    <row r="93" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B93" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" s="6"/>
+    </row>
+    <row r="94" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B94" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="6"/>
+    </row>
+    <row r="95" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B95" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A141">
+        <v>1</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A142">
+        <v>2</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A143">
+        <v>3</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A144">
+        <v>4</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A145">
+        <v>5</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A146">
+        <v>6</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A147">
+        <v>7</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A148">
+        <v>8</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A149">
+        <v>9</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A150">
+        <v>10</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A151">
+        <v>11</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A152">
+        <v>12</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A153">
+        <v>13</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A154">
+        <v>14</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A155">
+        <v>15</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A156">
+        <v>16</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A157">
+        <v>17</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A158">
+        <v>18</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A159">
+        <v>19</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>20</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>21</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A169">
+        <v>1</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A170">
+        <v>2</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B64" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="6"/>
-    </row>
-    <row r="65" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="6"/>
-    </row>
-    <row r="66" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B66" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="6"/>
-    </row>
-    <row r="67" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B67" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="6"/>
-    </row>
-    <row r="68" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B68" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="6"/>
-    </row>
-    <row r="69" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B69" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="6"/>
-    </row>
-    <row r="70" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B70" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="6"/>
-    </row>
-    <row r="71" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B71" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="6"/>
-    </row>
-    <row r="72" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B72" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A87">
-        <v>1</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A88">
-        <v>2</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A89">
+      <c r="C170" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A171">
         <v>3</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A90">
+      <c r="B171" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A172">
         <v>4</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A91">
+      <c r="B172" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A173">
         <v>5</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A92">
+      <c r="B173" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A174">
         <v>6</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A93">
+      <c r="B174" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A175">
         <v>7</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A94">
+      <c r="B175" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
+      <c r="A176">
         <v>8</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A95">
-        <v>9</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A96">
-        <v>10</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A97">
-        <v>11</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A98">
-        <v>12</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A99">
-        <v>13</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A100">
-        <v>14</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A101">
-        <v>15</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A102">
-        <v>16</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A103">
-        <v>17</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A104">
-        <v>18</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.7">
-      <c r="A105">
-        <v>19</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>20</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>21</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>21</v>
-      </c>
+      <c r="B176" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B179" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1798,43 +1949,52 @@
     <hyperlink ref="B54" r:id="rId54" xr:uid="{22B7693A-FFF7-42D9-AC11-FE795D2622A4}"/>
     <hyperlink ref="B55" r:id="rId55" xr:uid="{3ECBB2E5-0C54-40C7-B326-652B6610FDD5}"/>
     <hyperlink ref="B56" r:id="rId56" display="Container With Most Water" xr:uid="{7E3DEE61-5B25-4216-8AA3-39A04C5AAFE0}"/>
-    <hyperlink ref="B59" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
-    <hyperlink ref="B60" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
-    <hyperlink ref="B61" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
-    <hyperlink ref="B62" r:id="rId60" xr:uid="{93027393-03CE-4EB8-918E-F6F435C9B04B}"/>
-    <hyperlink ref="B63" r:id="rId61" xr:uid="{4A42692F-D72D-42DB-BE35-B30A9BDFEB16}"/>
-    <hyperlink ref="B64" r:id="rId62" xr:uid="{29C959BE-75F0-485B-B8C2-2FC68FD53868}"/>
-    <hyperlink ref="B65" r:id="rId63" xr:uid="{67087C73-7D08-48D0-9060-FA8E0F6A50AD}"/>
-    <hyperlink ref="B66" r:id="rId64" xr:uid="{54B91691-806E-4D1B-BCAD-710CB853A883}"/>
-    <hyperlink ref="B67" r:id="rId65" xr:uid="{468B0899-A951-4993-8E8A-342EA8E8F731}"/>
-    <hyperlink ref="B68" r:id="rId66" xr:uid="{25AAF2F4-1411-4145-80C4-A92DA586FC6C}"/>
-    <hyperlink ref="B69" r:id="rId67" xr:uid="{BB3105EF-EB98-4D41-B616-71A66E23CEF5}"/>
-    <hyperlink ref="B70" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
-    <hyperlink ref="B71" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
-    <hyperlink ref="B72" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
-    <hyperlink ref="B87" r:id="rId71" xr:uid="{CE309F08-AAC1-410D-8FF0-E7A7D5A30A1D}"/>
-    <hyperlink ref="B88" r:id="rId72" display="https://leetcode.com/problems/defanging-an-ip-address/" xr:uid="{61E13826-11D6-4ECB-BB7F-1CFA1CBC0F4A}"/>
-    <hyperlink ref="B89" r:id="rId73" xr:uid="{1A07F699-F5A6-4748-A976-593E0232604E}"/>
-    <hyperlink ref="B92" r:id="rId74" xr:uid="{2D3F5BC2-ED14-465B-9382-86BCCD107FD5}"/>
-    <hyperlink ref="B93" r:id="rId75" display="https://leetcode.com/problems/check-if-the-sentence-is-pangram/" xr:uid="{554A218C-8662-4AC2-8F6B-2BD542582755}"/>
-    <hyperlink ref="B94" r:id="rId76" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
-    <hyperlink ref="B95" r:id="rId77" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
-    <hyperlink ref="B96" r:id="rId78" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
-    <hyperlink ref="B98" r:id="rId79" display="Sum of two large numbers" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
-    <hyperlink ref="B99" r:id="rId80" display="13. Roman to Integer" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
-    <hyperlink ref="B102" r:id="rId81" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
-    <hyperlink ref="B103" r:id="rId82" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
-    <hyperlink ref="B104" r:id="rId83" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
-    <hyperlink ref="B105" r:id="rId84" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
-    <hyperlink ref="B106" r:id="rId85" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
-    <hyperlink ref="B107" r:id="rId86" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
-    <hyperlink ref="B97" r:id="rId87" display="https://leetcode.com/problems/sort-vowels-in-a-string/" xr:uid="{54E1491C-52FF-4A5F-919A-377E24189B75}"/>
-    <hyperlink ref="B100" r:id="rId88" display="https://leetcode.com/problems/integer-to-roman/" xr:uid="{87FF45BE-8E25-4645-9BEE-BF58CB0ACE49}"/>
-    <hyperlink ref="B101" r:id="rId89" xr:uid="{C73FEF19-EB93-4B48-8546-CC067904474D}"/>
-    <hyperlink ref="B57" r:id="rId90" display="https://leetcode.com/problems/median-of-two-sorted-arrays/" xr:uid="{A225C855-05F6-475F-9D5F-8F2E2142AF40}"/>
-    <hyperlink ref="B58" r:id="rId91" display="https://leetcode.com/problems/gas-station/" xr:uid="{B36E0DAE-16CC-42AF-82FD-1761D3574939}"/>
+    <hyperlink ref="B82" r:id="rId57" xr:uid="{BF13A896-416F-4267-81F0-62040EABF573}"/>
+    <hyperlink ref="B83" r:id="rId58" xr:uid="{6927D22C-B802-4091-BE35-55EF499D3F7F}"/>
+    <hyperlink ref="B84" r:id="rId59" xr:uid="{DA392EB0-2B39-4799-9750-B1C73B1E6485}"/>
+    <hyperlink ref="B85" r:id="rId60" xr:uid="{93027393-03CE-4EB8-918E-F6F435C9B04B}"/>
+    <hyperlink ref="B86" r:id="rId61" xr:uid="{4A42692F-D72D-42DB-BE35-B30A9BDFEB16}"/>
+    <hyperlink ref="B87" r:id="rId62" xr:uid="{29C959BE-75F0-485B-B8C2-2FC68FD53868}"/>
+    <hyperlink ref="B88" r:id="rId63" xr:uid="{67087C73-7D08-48D0-9060-FA8E0F6A50AD}"/>
+    <hyperlink ref="B89" r:id="rId64" xr:uid="{54B91691-806E-4D1B-BCAD-710CB853A883}"/>
+    <hyperlink ref="B90" r:id="rId65" xr:uid="{468B0899-A951-4993-8E8A-342EA8E8F731}"/>
+    <hyperlink ref="B91" r:id="rId66" xr:uid="{25AAF2F4-1411-4145-80C4-A92DA586FC6C}"/>
+    <hyperlink ref="B92" r:id="rId67" xr:uid="{BB3105EF-EB98-4D41-B616-71A66E23CEF5}"/>
+    <hyperlink ref="B93" r:id="rId68" xr:uid="{846F7ECF-E44E-4A3A-869E-C110A19E148F}"/>
+    <hyperlink ref="B94" r:id="rId69" xr:uid="{9AFBCE84-5B82-4261-B638-011B676781B5}"/>
+    <hyperlink ref="B95" r:id="rId70" xr:uid="{6D70321C-2E97-4678-A0BA-6F77723BD753}"/>
+    <hyperlink ref="B142" r:id="rId71" display="https://leetcode.com/problems/defanging-an-ip-address/" xr:uid="{61E13826-11D6-4ECB-BB7F-1CFA1CBC0F4A}"/>
+    <hyperlink ref="B143" r:id="rId72" xr:uid="{1A07F699-F5A6-4748-A976-593E0232604E}"/>
+    <hyperlink ref="B146" r:id="rId73" xr:uid="{2D3F5BC2-ED14-465B-9382-86BCCD107FD5}"/>
+    <hyperlink ref="B147" r:id="rId74" display="https://leetcode.com/problems/check-if-the-sentence-is-pangram/" xr:uid="{554A218C-8662-4AC2-8F6B-2BD542582755}"/>
+    <hyperlink ref="B148" r:id="rId75" xr:uid="{F2C85DEE-F083-47AA-AA9E-215537AF69B8}"/>
+    <hyperlink ref="B149" r:id="rId76" display="https://leetcode.com/problems/longest-palindrome/" xr:uid="{A8C0E4F6-8790-4E09-B9C7-12AE4A10AE40}"/>
+    <hyperlink ref="B150" r:id="rId77" display="https://leetcode.com/problems/sorting-the-sentence/" xr:uid="{7A60F71F-DE36-49A0-9B1F-6E29CFF65EA7}"/>
+    <hyperlink ref="B152" r:id="rId78" display="Sum of two large numbers" xr:uid="{E77A0893-9F79-4CFB-A127-CD5E448C2128}"/>
+    <hyperlink ref="B153" r:id="rId79" display="13. Roman to Integer" xr:uid="{8DEF6DC7-3D1E-4EA6-8B69-8BAA1C75F281}"/>
+    <hyperlink ref="B156" r:id="rId80" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/" xr:uid="{B0269EDB-F02A-424C-BF93-BA4F5408D966}"/>
+    <hyperlink ref="B157" r:id="rId81" xr:uid="{23658ABB-E75E-4DA0-BB2D-6F3E5D967D3F}"/>
+    <hyperlink ref="B158" r:id="rId82" display="Longest Prefix Suffix" xr:uid="{2B90503B-0852-45DF-9D20-BAE27C95DBD1}"/>
+    <hyperlink ref="B159" r:id="rId83" display="https://leetcode.com/problems/find-the-index-of-the-first-occurrence-in-a-string/" xr:uid="{D2052AD1-396C-45A7-B0BD-74B8AD77309A}"/>
+    <hyperlink ref="B160" r:id="rId84" xr:uid="{FCABE85A-7B0F-4DE8-9B01-D6347339273E}"/>
+    <hyperlink ref="B161" r:id="rId85" display="https://leetcode.com/problems/repeated-string-match/" xr:uid="{5EC289B4-F36C-4508-BEDB-E0C7CEAFB276}"/>
+    <hyperlink ref="B151" r:id="rId86" display="https://leetcode.com/problems/sort-vowels-in-a-string/" xr:uid="{54E1491C-52FF-4A5F-919A-377E24189B75}"/>
+    <hyperlink ref="B154" r:id="rId87" display="https://leetcode.com/problems/integer-to-roman/" xr:uid="{87FF45BE-8E25-4645-9BEE-BF58CB0ACE49}"/>
+    <hyperlink ref="B155" r:id="rId88" xr:uid="{C73FEF19-EB93-4B48-8546-CC067904474D}"/>
+    <hyperlink ref="B57" r:id="rId89" display="https://leetcode.com/problems/median-of-two-sorted-arrays/" xr:uid="{A225C855-05F6-475F-9D5F-8F2E2142AF40}"/>
+    <hyperlink ref="B58" r:id="rId90" display="https://leetcode.com/problems/gas-station/" xr:uid="{B36E0DAE-16CC-42AF-82FD-1761D3574939}"/>
+    <hyperlink ref="B169" r:id="rId91" xr:uid="{4EBCC1A9-191B-4061-AC00-C42C3C5E145B}"/>
+    <hyperlink ref="B170" r:id="rId92" xr:uid="{37540B0E-DA0F-485F-A43D-19697CCAD170}"/>
+    <hyperlink ref="B171" r:id="rId93" xr:uid="{B0E48173-3EBB-4F50-B68E-A2BD7374F15E}"/>
+    <hyperlink ref="B172" r:id="rId94" xr:uid="{2955B299-EBCD-4463-97C0-F8850FF9DDAB}"/>
+    <hyperlink ref="B173" r:id="rId95" xr:uid="{F9CB4E3A-A7FE-4F3B-AD61-D9E427ED77ED}"/>
+    <hyperlink ref="B174" r:id="rId96" xr:uid="{F802D24A-5A50-43B7-BA59-CCAC834A761F}"/>
+    <hyperlink ref="B175" r:id="rId97" xr:uid="{7BA02618-44CC-45F4-87AF-C5C1DC3B000A}"/>
+    <hyperlink ref="B176" r:id="rId98" xr:uid="{A1F16112-63F9-4A58-ABA2-32EBEBA9952C}"/>
+    <hyperlink ref="B141" r:id="rId99" xr:uid="{CE309F08-AAC1-410D-8FF0-E7A7D5A30A1D}"/>
+    <hyperlink ref="B59" r:id="rId100" xr:uid="{E354C408-16AD-4C6C-A697-B851D5EF0997}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId92"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId101"/>
 </worksheet>
 </file>